--- a/exports/health_report_weekly_20260616.xlsx
+++ b/exports/health_report_weekly_20260616.xlsx
@@ -509,7 +509,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>4 条</t>
+          <t>3 条</t>
         </is>
       </c>
     </row>
@@ -521,7 +521,7 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>11 条</t>
+          <t>12 条</t>
         </is>
       </c>
     </row>
@@ -533,7 +533,7 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>11 个</t>
+          <t>12 个</t>
         </is>
       </c>
     </row>
@@ -617,10 +617,10 @@
         <v>15</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -660,7 +660,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3">
@@ -894,7 +894,7 @@
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 18:24:19</t>
+          <t>2026-06-16 19:00:13</t>
         </is>
       </c>
     </row>
@@ -929,7 +929,7 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 18:24:19</t>
+          <t>2026-06-16 19:00:13</t>
         </is>
       </c>
     </row>
@@ -964,7 +964,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 18:24:19</t>
+          <t>2026-06-16 19:00:13</t>
         </is>
       </c>
     </row>
@@ -984,12 +984,12 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>warning</t>
+          <t>critical</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>[警告] app-server-01 网络带宽容量预警</t>
+          <t>[严重] app-server-01 网络带宽容量预警</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
@@ -999,7 +999,7 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 18:24:19</t>
+          <t>2026-06-16 19:00:13</t>
         </is>
       </c>
     </row>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 18:24:19</t>
+          <t>2026-06-16 19:00:13</t>
         </is>
       </c>
     </row>
@@ -1069,7 +1069,7 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 18:24:19</t>
+          <t>2026-06-16 19:00:13</t>
         </is>
       </c>
     </row>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 18:24:19</t>
+          <t>2026-06-16 19:00:13</t>
         </is>
       </c>
     </row>
@@ -1139,7 +1139,7 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 18:24:19</t>
+          <t>2026-06-16 19:00:13</t>
         </is>
       </c>
     </row>
@@ -1174,7 +1174,7 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 18:24:19</t>
+          <t>2026-06-16 19:00:13</t>
         </is>
       </c>
     </row>
@@ -1209,7 +1209,7 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 18:24:19</t>
+          <t>2026-06-16 19:00:13</t>
         </is>
       </c>
     </row>
@@ -1244,7 +1244,7 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 18:24:19</t>
+          <t>2026-06-16 19:00:13</t>
         </is>
       </c>
     </row>
@@ -1279,7 +1279,7 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 18:24:19</t>
+          <t>2026-06-16 19:00:13</t>
         </is>
       </c>
     </row>
@@ -1314,7 +1314,7 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 18:24:19</t>
+          <t>2026-06-16 19:00:13</t>
         </is>
       </c>
     </row>
@@ -1349,7 +1349,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 18:24:19</t>
+          <t>2026-06-16 19:00:13</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>critical</t>
+          <t>fatal</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>[严重] web-server-01 CPU容量预警</t>
+          <t>[致命] web-server-01 CPU容量预警</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 18:24:19</t>
+          <t>2026-06-16 19:00:13</t>
         </is>
       </c>
     </row>
